--- a/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-50_p-10_nm_basis-False_nm_modifier-False.xlsx
+++ b/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-50_p-10_nm_basis-False_nm_modifier-False.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,609 +448,324 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sub6ex1</t>
+          <t>sub1ex1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>83.45167345738284</v>
+        <v>79.00085640879247</v>
       </c>
       <c r="C2" t="n">
-        <v>83.25210073782638</v>
+        <v>78.74028710053719</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4698810532611484</v>
+        <v>0.5921736466387908</v>
       </c>
       <c r="E2" t="n">
-        <v>83.45167345738284</v>
+        <v>79.00085640879246</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sub6ex2</t>
+          <t>sub1ex2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>84.42996911737991</v>
+        <v>72.73427970830198</v>
       </c>
       <c r="C3" t="n">
-        <v>84.10290512068923</v>
+        <v>72.6038271637736</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4685707478163142</v>
+        <v>0.7166669440766176</v>
       </c>
       <c r="E3" t="n">
-        <v>84.42996911737991</v>
+        <v>72.73427970830197</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sub6ex3</t>
+          <t>sub1ex3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>85.13291637470913</v>
+        <v>70.12923987231724</v>
       </c>
       <c r="C4" t="n">
-        <v>84.7653769202221</v>
+        <v>69.80820812184841</v>
       </c>
       <c r="D4" t="n">
-        <v>0.410366279030374</v>
+        <v>0.7625677391886712</v>
       </c>
       <c r="E4" t="n">
-        <v>85.13291637470913</v>
+        <v>70.12923987231724</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sub7ex1</t>
+          <t>sub2ex1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77.13250114620368</v>
+        <v>79.00189448005605</v>
       </c>
       <c r="C5" t="n">
-        <v>77.2571062337305</v>
+        <v>78.70908457233426</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6065410929421584</v>
+        <v>0.5355210850015283</v>
       </c>
       <c r="E5" t="n">
-        <v>77.13250114620368</v>
+        <v>79.00189448005605</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sub7ex2</t>
+          <t>sub2ex2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>77.43233072950457</v>
+        <v>76.03967162345695</v>
       </c>
       <c r="C6" t="n">
-        <v>77.2153476994566</v>
+        <v>75.16814636295692</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6287011046738674</v>
+        <v>0.7005775503193339</v>
       </c>
       <c r="E6" t="n">
-        <v>77.43233072950457</v>
+        <v>76.03967162345695</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sub7ex3</t>
+          <t>sub2ex3</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>73.75773146826529</v>
+        <v>78.38415557228004</v>
       </c>
       <c r="C7" t="n">
-        <v>73.71966545832889</v>
+        <v>77.86836471699441</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6916353484615684</v>
+        <v>0.5003246776759624</v>
       </c>
       <c r="E7" t="n">
-        <v>73.75773146826529</v>
+        <v>78.38415557228004</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sub8ex1</t>
+          <t>sub3ex1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>83.52312736269344</v>
+        <v>66.77851884531873</v>
       </c>
       <c r="C8" t="n">
-        <v>83.23820836119494</v>
+        <v>66.26632408852895</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3978905904863496</v>
+        <v>0.8994676175216834</v>
       </c>
       <c r="E8" t="n">
-        <v>83.52312736269344</v>
+        <v>66.77851884531873</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sub8ex2</t>
+          <t>sub3ex2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82.95478334587669</v>
+        <v>75.82764556786825</v>
       </c>
       <c r="C9" t="n">
-        <v>81.95620851100671</v>
+        <v>74.53454580757784</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5436244626374295</v>
+        <v>0.7390686163057885</v>
       </c>
       <c r="E9" t="n">
-        <v>82.95478334587669</v>
+        <v>75.82764556786825</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sub8ex3</t>
+          <t>sub3ex3</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90.41453645792784</v>
+        <v>81.07163556778173</v>
       </c>
       <c r="C10" t="n">
-        <v>90.4920425795751</v>
+        <v>80.66842740869586</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2396406759546759</v>
+        <v>0.496185373608023</v>
       </c>
       <c r="E10" t="n">
-        <v>90.41453645792784</v>
+        <v>81.07163556778173</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sub9ex1</t>
+          <t>sub4ex1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>87.8486838121437</v>
+        <v>72.62199499995674</v>
       </c>
       <c r="C11" t="n">
-        <v>87.74172131125165</v>
+        <v>72.00184643937807</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3541497274069115</v>
+        <v>0.8308063428228101</v>
       </c>
       <c r="E11" t="n">
-        <v>87.8486838121437</v>
+        <v>72.62199499995674</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sub9ex2</t>
+          <t>sub4ex2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>81.56497893580395</v>
+        <v>64.10513931781416</v>
       </c>
       <c r="C12" t="n">
-        <v>81.18650550447963</v>
+        <v>64.14254320020915</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5101704405620694</v>
+        <v>0.8900365111728508</v>
       </c>
       <c r="E12" t="n">
-        <v>81.56497893580395</v>
+        <v>64.10513931781416</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sub9ex3</t>
+          <t>sub4ex3</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>84.77261914030399</v>
+        <v>71.89344198479225</v>
       </c>
       <c r="C13" t="n">
-        <v>84.1927924982103</v>
+        <v>71.71144943135957</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4858859964335958</v>
+        <v>0.6917877402156591</v>
       </c>
       <c r="E13" t="n">
-        <v>84.77261914030399</v>
+        <v>71.89344198479225</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sub10ex1</t>
+          <t>sub5ex1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>78.50785906452478</v>
+        <v>71.47362866460783</v>
       </c>
       <c r="C14" t="n">
-        <v>78.01738969223999</v>
+        <v>70.6862006772042</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5572547089308501</v>
+        <v>0.7757422506809235</v>
       </c>
       <c r="E14" t="n">
-        <v>78.50785906452478</v>
+        <v>71.47362866460783</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sub10ex2</t>
+          <t>sub5ex2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>82.03678232510661</v>
+        <v>71.86792273289561</v>
       </c>
       <c r="C15" t="n">
-        <v>81.81254053936387</v>
+        <v>71.05894126879863</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4737694282705586</v>
+        <v>0.8239245928823948</v>
       </c>
       <c r="E15" t="n">
-        <v>82.03678232510661</v>
+        <v>71.86792273289561</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sub10ex3</t>
+          <t>sub5ex3</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>75.17296862429606</v>
+        <v>70.94602894488706</v>
       </c>
       <c r="C16" t="n">
-        <v>74.83667715251667</v>
+        <v>71.30523545095903</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6607421075304349</v>
+        <v>0.808570042764768</v>
       </c>
       <c r="E16" t="n">
-        <v>75.17296862429606</v>
+        <v>70.94602894488708</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sub11ex1</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>82.12648898346872</v>
+        <v>73.45840361940849</v>
       </c>
       <c r="C17" t="n">
-        <v>81.81382865675749</v>
+        <v>73.01822878741041</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4774995462968946</v>
+        <v>0.717561382058387</v>
       </c>
       <c r="E17" t="n">
-        <v>82.1264889834687</v>
+        <v>73.45840361940849</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sub11ex2</t>
+          <t>Std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>82.33799600342563</v>
+        <v>4.586875705183816</v>
       </c>
       <c r="C18" t="n">
-        <v>81.7397095727719</v>
+        <v>4.501056902380551</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4805001894477755</v>
+        <v>0.1283599713024269</v>
       </c>
       <c r="E18" t="n">
-        <v>82.33799600342563</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>sub11ex3</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>86.69703025112673</v>
-      </c>
-      <c r="C19" t="n">
-        <v>86.7387370040599</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.3558883283597728</v>
-      </c>
-      <c r="E19" t="n">
-        <v>86.69703025112673</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>sub12ex1</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>77.63068884678933</v>
-      </c>
-      <c r="C20" t="n">
-        <v>77.34048084128075</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.6003315043946107</v>
-      </c>
-      <c r="E20" t="n">
-        <v>77.63068884678934</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>sub12ex2</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>68.26996773328489</v>
-      </c>
-      <c r="C21" t="n">
-        <v>67.28644580124198</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.8379430552381868</v>
-      </c>
-      <c r="E21" t="n">
-        <v>68.2699677332849</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>sub12ex3</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>77.44435505497452</v>
-      </c>
-      <c r="C22" t="n">
-        <v>77.05949777009339</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.5866645071655512</v>
-      </c>
-      <c r="E22" t="n">
-        <v>77.44435505497452</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>sub13ex1</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>76.06882412477617</v>
-      </c>
-      <c r="C23" t="n">
-        <v>75.4154570316379</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.6634436499327421</v>
-      </c>
-      <c r="E23" t="n">
-        <v>76.06882412477617</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>sub13ex2</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>84.19207778614002</v>
-      </c>
-      <c r="C24" t="n">
-        <v>84.08194448345893</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.4335328261523198</v>
-      </c>
-      <c r="E24" t="n">
-        <v>84.19207778614002</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>sub13ex3</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>80.92552703743112</v>
-      </c>
-      <c r="C25" t="n">
-        <v>80.83290119198747</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.4951791894001265</v>
-      </c>
-      <c r="E25" t="n">
-        <v>80.92552703743112</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>sub14ex1</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>81.75183176325055</v>
-      </c>
-      <c r="C26" t="n">
-        <v>81.49323437146104</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.4652452325603614</v>
-      </c>
-      <c r="E26" t="n">
-        <v>81.75183176325055</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>sub14ex2</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>72.17259664875994</v>
-      </c>
-      <c r="C27" t="n">
-        <v>72.12783717294219</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.7891272295344</v>
-      </c>
-      <c r="E27" t="n">
-        <v>72.17259664875994</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>sub14ex3</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>79.41297070043859</v>
-      </c>
-      <c r="C28" t="n">
-        <v>79.11243862801983</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.5849222862472137</v>
-      </c>
-      <c r="E28" t="n">
-        <v>79.41297070043859</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>sub15ex1</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>90.20700871114802</v>
-      </c>
-      <c r="C29" t="n">
-        <v>90.23260085305856</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.2905508880813917</v>
-      </c>
-      <c r="E29" t="n">
-        <v>90.20700871114802</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>sub15ex2</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>91.06523412832291</v>
-      </c>
-      <c r="C30" t="n">
-        <v>91.05208729191577</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.2613690863082108</v>
-      </c>
-      <c r="E30" t="n">
-        <v>91.06523412832291</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>sub15ex3</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>92.6854038529745</v>
-      </c>
-      <c r="C31" t="n">
-        <v>92.36323946224005</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.2209346183013016</v>
-      </c>
-      <c r="E31" t="n">
-        <v>92.6854038529745</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>81.70404876628113</v>
-      </c>
-      <c r="C32" t="n">
-        <v>81.41590094843399</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.5013985300606387</v>
-      </c>
-      <c r="E32" t="n">
-        <v>81.70404876628113</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Std</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>5.660825014700567</v>
-      </c>
-      <c r="C33" t="n">
-        <v>5.756263935377371</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.148470283076845</v>
-      </c>
-      <c r="E33" t="n">
-        <v>5.660825014700565</v>
+        <v>4.586875705183815</v>
       </c>
     </row>
   </sheetData>
@@ -1096,16 +811,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81.70404876628113</v>
+        <v>73.45840361940849</v>
       </c>
       <c r="B2" t="n">
-        <v>81.41590094843399</v>
+        <v>73.01822878741041</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5013985300606387</v>
+        <v>0.717561382058387</v>
       </c>
       <c r="D2" t="n">
-        <v>81.70404876628113</v>
+        <v>73.45840361940849</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1115,16 +830,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5.660825014700567</v>
+        <v>4.586875705183816</v>
       </c>
       <c r="B3" t="n">
-        <v>5.756263935377371</v>
+        <v>4.501056902380551</v>
       </c>
       <c r="C3" t="n">
-        <v>0.148470283076845</v>
+        <v>0.1283599713024269</v>
       </c>
       <c r="D3" t="n">
-        <v>5.660825014700565</v>
+        <v>4.586875705183815</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1190,28 +905,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81.70404876628113</v>
+        <v>73.45840361940849</v>
       </c>
       <c r="B2" t="n">
-        <v>5.660825014700567</v>
+        <v>4.586875705183816</v>
       </c>
       <c r="C2" t="n">
-        <v>81.41590094843399</v>
+        <v>73.01822878741041</v>
       </c>
       <c r="D2" t="n">
-        <v>5.756263935377371</v>
+        <v>4.501056902380551</v>
       </c>
       <c r="E2" t="n">
-        <v>81.70404876628113</v>
+        <v>73.45840361940849</v>
       </c>
       <c r="F2" t="n">
-        <v>5.660825014700565</v>
+        <v>4.586875705183815</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5013985300606387</v>
+        <v>0.717561382058387</v>
       </c>
       <c r="H2" t="n">
-        <v>0.148470283076845</v>
+        <v>0.1283599713024269</v>
       </c>
     </row>
   </sheetData>
